--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>157</v>
+        <v>32</v>
       </c>
       <c r="D2">
-        <v>126</v>
+        <v>379</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>140</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="D3">
-        <v>351</v>
+        <v>253</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="D3">
         <v>253</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>
